--- a/tumores/4. Orofaringe (p16-).xlsx
+++ b/tumores/4. Orofaringe (p16-).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EA31A3-AFA0-4FA8-97B8-505639FD7892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E49C4-F0E0-4A31-8516-BB97DCBA8BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="8520" windowHeight="8880" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -109,12 +109,6 @@
     <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
-    <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>≤3 cm y ENE+, &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -130,12 +124,6 @@
     <t>Ganglio ipsilateral &gt;3 cm ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>Ganglio/s linfáticos con ENE+ </t>
   </si>
   <si>
@@ -157,24 +145,6 @@
     <t xml:space="preserve"> ≤2 cm</t>
   </si>
   <si>
-    <t>&gt;2 cm y ≤4 cm</t>
-  </si>
-  <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Contralaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Bilaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;3 cm , Multiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
-  </si>
-  <si>
     <t>Sin metástasis</t>
   </si>
   <si>
@@ -250,18 +220,12 @@
     <t>🟨 N2a: Un ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟨 N2b: Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟨 N2c: Ganglios contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
     <t>🟨 N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦 N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟦 N3b: Uno o más ganglios con ENE+</t>
   </si>
   <si>
@@ -296,6 +260,42 @@
   </si>
   <si>
     <t>Laringe, Músculo extrínseco de la lengua, Pterigoideo medial, Paladar duro, Mandíbula</t>
+  </si>
+  <si>
+    <t>Entre 2 cm y 4 cm</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>G.Contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>G.Bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟨 N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟦 N3a: Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
   </si>
 </sst>
 </file>
@@ -830,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>9</v>
@@ -839,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -867,7 +867,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -883,14 +883,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -899,14 +899,14 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -915,14 +915,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -931,14 +931,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -947,16 +947,16 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -965,10 +965,10 @@
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>13</v>
@@ -983,7 +983,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>17</v>
@@ -1000,13 +1000,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
@@ -1034,13 +1034,13 @@
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1051,13 +1051,13 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1068,13 +1068,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1085,13 +1085,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1102,13 +1102,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1119,14 +1119,14 @@
         <v>15</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1137,7 +1137,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>17</v>
@@ -1154,13 +1154,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1171,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>19</v>
@@ -1188,16 +1188,16 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1208,13 +1208,13 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1225,13 +1225,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1242,16 +1242,16 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -1259,13 +1259,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1276,44 +1276,44 @@
         <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1342,10 +1342,10 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1356,7 +1356,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1384,10 +1384,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1398,24 +1398,24 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1423,27 +1423,27 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -1451,27 +1451,27 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1479,27 +1479,27 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/4. Orofaringe (p16-).xlsx
+++ b/tumores/4. Orofaringe (p16-).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E49C4-F0E0-4A31-8516-BB97DCBA8BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4F9610-9D71-4E5F-9E0C-2EB1E33CC7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -202,12 +202,6 @@
     <t>🟨 T2: &gt;2 cm pero ≤4 cm</t>
   </si>
   <si>
-    <t>🟥 T4b: Enfermedad muy avanzada *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inv. </t>
-  </si>
-  <si>
     <t>NX: Ganglios no evaluables</t>
   </si>
   <si>
@@ -250,18 +244,9 @@
     <t>&gt;4 cm</t>
   </si>
   <si>
-    <t>🟥 T4a: Invasión moderada *</t>
-  </si>
-  <si>
-    <t>Pterigoideo lateral, Placas pterigoideas, Nasofaringe lateral, Base del cráneo, Atrapamiento de carótida</t>
-  </si>
-  <si>
     <t>🟦 N3b: Uno o varios ganglios ENE+ *</t>
   </si>
   <si>
-    <t>Laringe, Músculo extrínseco de la lengua, Pterigoideo medial, Paladar duro, Mandíbula</t>
-  </si>
-  <si>
     <t>Entre 2 cm y 4 cm</t>
   </si>
   <si>
@@ -296,6 +281,21 @@
   </si>
   <si>
     <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟥 T4a: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t>Invasión de Laringe, Invasión de Músculo extrínseco de la lengua, Invasión de Pterigoideo medial, Invasión de Paladar duro, Invasión de Mandíbula</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Pterigoideo lateral, Apófisis pterigoides, Nasofaringe lateral, Base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -915,14 +915,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -931,14 +931,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -947,16 +947,16 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -964,11 +964,11 @@
         <v>0</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>58</v>
+      <c r="C9" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>13</v>
@@ -983,7 +983,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>17</v>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>18</v>
@@ -1017,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
@@ -1034,7 +1034,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>20</v>
@@ -1051,13 +1051,13 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1068,13 +1068,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1085,13 +1085,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1102,13 +1102,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1119,7 +1119,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
@@ -1137,7 +1137,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>17</v>
@@ -1154,7 +1154,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>18</v>
@@ -1171,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>19</v>
@@ -1188,7 +1188,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>27</v>
@@ -1208,13 +1208,13 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1225,13 +1225,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1242,13 +1242,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1259,13 +1259,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1276,10 +1276,10 @@
         <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>24</v>
@@ -1293,7 +1293,7 @@
         <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>34</v>
@@ -1307,7 +1307,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>35</v>

--- a/tumores/4. Orofaringe (p16-).xlsx
+++ b/tumores/4. Orofaringe (p16-).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4F9610-9D71-4E5F-9E0C-2EB1E33CC7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7192CC8-C530-4F32-8E68-D1EBCC60E19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -289,13 +289,13 @@
     <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
   </si>
   <si>
-    <t>Invasión de Laringe, Invasión de Músculo extrínseco de la lengua, Invasión de Pterigoideo medial, Invasión de Paladar duro, Invasión de Mandíbula</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Pterigoideo lateral, Apófisis pterigoides, Nasofaringe lateral, Base del cráneo, Envuelve la carótida interna</t>
+    <t>Invasión de laringe, Invasión de músculo extrínseco de la lengua, Invasión de pterigoideo medial, Invasión de paladar duro, Invasión de mandíbula</t>
+  </si>
+  <si>
+    <t>Invasión de pterigoideo lateral, Invasión de apófisis pterigoides, Invasión de nasofaringe lateral, Invasión de base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="40" style="5" customWidth="1"/>
     <col min="5" max="5" width="27.21875" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" style="5" customWidth="1"/>
     <col min="7" max="16384" width="11.5546875" style="5"/>
@@ -950,13 +950,13 @@
         <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1268,7 +1268,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>14</v>
       </c>

--- a/tumores/4. Orofaringe (p16-).xlsx
+++ b/tumores/4. Orofaringe (p16-).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7192CC8-C530-4F32-8E68-D1EBCC60E19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0F6070-F729-4FBB-A9C4-FB5915F1D175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -1180,7 +1180,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>14</v>
       </c>
